--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260524_204456.xlsx
@@ -5608,7 +5608,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
